--- a/Project_ETF/ETF_Investment_Portfolio/00878/ETF_Investment_Portfolio_20260811.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00878/ETF_Investment_Portfolio_20260811.xlsx
@@ -616,7 +616,7 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>9.87%</t>
+          <t>9.88%</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>8.95%</t>
+          <t>8.98%</t>
         </is>
       </c>
     </row>
@@ -660,7 +660,7 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>6.02%</t>
+          <t>5.92%</t>
         </is>
       </c>
     </row>
@@ -682,7 +682,7 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>5.13%</t>
+          <t>5.25%</t>
         </is>
       </c>
     </row>
@@ -704,7 +704,7 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>3.79%</t>
+          <t>3.85%</t>
         </is>
       </c>
     </row>
@@ -726,7 +726,7 @@
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>3.71%</t>
+          <t>3.70%</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>3.53%</t>
+          <t>3.48%</t>
         </is>
       </c>
     </row>
@@ -770,7 +770,7 @@
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>3.34%</t>
+          <t>3.40%</t>
         </is>
       </c>
     </row>
@@ -792,7 +792,7 @@
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>3.22%</t>
+          <t>3.26%</t>
         </is>
       </c>
     </row>
@@ -809,12 +809,12 @@
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>448,725,000</t>
+          <t>454,725,000</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>3.19%</t>
+          <t>3.20%</t>
         </is>
       </c>
     </row>
@@ -853,12 +853,12 @@
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>362,939,964</t>
+          <t>364,639,964</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>2.99%</t>
+          <t>2.90%</t>
         </is>
       </c>
     </row>
@@ -880,51 +880,51 @@
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>2.77%</t>
+          <t>2.73%</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>3034</t>
+          <t>2881</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>聯詠</t>
+          <t>富邦金</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>31,356,000</t>
+          <t>131,819,945</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>2.76%</t>
+          <t>2.72%</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>2881</t>
+          <t>3034</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>富邦金</t>
+          <t>聯詠</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>131,819,945</t>
+          <t>31,356,000</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>2.74%</t>
+          <t>2.72%</t>
         </is>
       </c>
     </row>
@@ -946,7 +946,7 @@
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>2.66%</t>
+          <t>2.65%</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>2.58%</t>
+          <t>2.55%</t>
         </is>
       </c>
     </row>
@@ -1034,7 +1034,7 @@
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>2.47%</t>
+          <t>2.48%</t>
         </is>
       </c>
     </row>
@@ -1056,7 +1056,7 @@
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>2.39%</t>
+          <t>2.37%</t>
         </is>
       </c>
     </row>
@@ -1078,51 +1078,51 @@
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>2.36%</t>
+          <t>2.33%</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>2412</t>
+          <t>4958</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>中華電</t>
+          <t>臻鼎-KY</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>99,617,000</t>
+          <t>28,764,000</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>2.20%</t>
+          <t>2.27%</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>4958</t>
+          <t>2412</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>臻鼎-KY</t>
+          <t>中華電</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>28,764,000</t>
+          <t>99,617,000</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>2.19%</t>
+          <t>2.18%</t>
         </is>
       </c>
     </row>
@@ -1166,7 +1166,7 @@
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>2.01%</t>
+          <t>1.97%</t>
         </is>
       </c>
     </row>
@@ -1188,51 +1188,51 @@
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>1.96%</t>
+          <t>1.95%</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>2618</t>
+          <t>3293</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>長榮航</t>
+          <t>鈊  象</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>273,066,000</t>
+          <t>14,253,000</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>1.88%</t>
+          <t>1.85%</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>3293</t>
+          <t>2618</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>鈊  象</t>
+          <t>長榮航</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>14,253,000</t>
+          <t>273,066,000</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>1.82%</t>
+          <t>1.84%</t>
         </is>
       </c>
     </row>
@@ -1254,7 +1254,7 @@
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>1.82%</t>
+          <t>1.81%</t>
         </is>
       </c>
     </row>
@@ -1276,7 +1276,7 @@
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>1.63%</t>
+          <t>1.72%</t>
         </is>
       </c>
     </row>
@@ -1293,7 +1293,7 @@
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>13,830,852,234</t>
+          <t>13,969,775,538</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr"/>
@@ -1311,7 +1311,7 @@
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>4,640,381,183</t>
+          <t>4,679,445,183</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr"/>
@@ -1329,7 +1329,7 @@
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>-22,447,244</t>
+          <t>-45,859,339</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr"/>
